--- a/output/resultado_impacto_tarifas_agregado_montante.xlsx
+++ b/output/resultado_impacto_tarifas_agregado_montante.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\tarifas_setor_eletrico\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC004E0-784E-489C-BDA3-C4A140FA2BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BF78FB-C8B0-42DE-90CE-A9388EB7C373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1410" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>Grupo</t>
   </si>
@@ -52,19 +52,34 @@
     <t>Renda/Gênero/Raça</t>
   </si>
   <si>
+    <t>Mulher negra (renda alta)</t>
+  </si>
+  <si>
     <t>Homem branco (renda média)</t>
   </si>
   <si>
     <t>Homem branco (renda alta)</t>
   </si>
   <si>
+    <t>Mulher branca (renda média)</t>
+  </si>
+  <si>
     <t>Mulher branca (renda alta)</t>
+  </si>
+  <si>
+    <t>Homem negro (renda alta)</t>
+  </si>
+  <si>
+    <t>Homem negro (renda média)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -107,7 +122,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -413,14 +428,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -499,13 +513,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <v>12403859.10507361</v>
+        <v>1231282.9287523001</v>
       </c>
       <c r="D5" s="2">
-        <v>18.399935880038271</v>
+        <v>27.45422748955426</v>
       </c>
       <c r="E5" s="2">
-        <v>228.2302121983833</v>
+        <v>33.803921629970283</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -516,13 +530,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="3">
-        <v>4439841.7067329204</v>
+        <v>12403859.10507361</v>
       </c>
       <c r="D6" s="2">
-        <v>24.032979600286069</v>
+        <v>18.399935880038271</v>
       </c>
       <c r="E6" s="2">
-        <v>106.70262516641159</v>
+        <v>228.2302121983833</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -533,13 +547,81 @@
         <v>9</v>
       </c>
       <c r="C7" s="3">
+        <v>4439841.7067329204</v>
+      </c>
+      <c r="D7" s="2">
+        <v>24.032979600286069</v>
+      </c>
+      <c r="E7" s="2">
+        <v>106.70262516641159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3">
+        <v>8444715.21531941</v>
+      </c>
+      <c r="D8" s="2">
+        <v>18.226392764667171</v>
+      </c>
+      <c r="E8" s="2">
+        <v>153.91669630017239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3">
         <v>3221820.9180313898</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D9" s="2">
         <v>21.312656507326381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E9" s="2">
         <v>68.665562554121962</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2064143.5564383499</v>
+      </c>
+      <c r="D10" s="2">
+        <v>22.949013055007899</v>
+      </c>
+      <c r="E10" s="2">
+        <v>47.370057424114123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3">
+        <v>16215420.710460929</v>
+      </c>
+      <c r="D11" s="2">
+        <v>18.748409936247629</v>
+      </c>
+      <c r="E11" s="2">
+        <v>304.01335476844122</v>
       </c>
     </row>
   </sheetData>

--- a/output/resultado_impacto_tarifas_agregado_montante.xlsx
+++ b/output/resultado_impacto_tarifas_agregado_montante.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\tarifas_setor_eletrico\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BF78FB-C8B0-42DE-90CE-A9388EB7C373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026F531E-D948-4E09-AC9B-F78BEA9B1730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -432,9 +432,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
